--- a/WorkBot/refactor/data/orders/Sysco/CompletedOrders/Sysco_Collegetown_2025-10-08.xlsx
+++ b/WorkBot/refactor/data/orders/Sysco/CompletedOrders/Sysco_Collegetown_2025-10-08.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,303 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7715362</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cleaner - Oven &amp; Grill (arsl)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>47.75</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>47.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4136768</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PKT Ketchup</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2393502</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>English Muffin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2072536</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Frz Orange Juice</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>104.13</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>104.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3438393</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cakerie - Cake Chocolate Dreamin' GF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>78.99</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>78.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1956804</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Asiago (Shredded)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>57.85</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>57.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5756060</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SABRA - Hummus Roasted Garlic With Pretzels</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>32.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7468531</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gatorade Cool Blue</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7468515</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gatorade Fruit Punch</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7468556</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gatorade Orange</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>29.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7119269</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Naked - Green Machine</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
